--- a/Datas/Skill3KP.xlsx
+++ b/Datas/Skill3KP.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>##var</t>
   </si>
@@ -37,6 +37,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>Duration</t>
+  </si>
+  <si>
     <t>DamageMultiplier</t>
   </si>
   <si>
@@ -68,6 +71,9 @@
   </si>
   <si>
     <t>参数ID</t>
+  </si>
+  <si>
+    <t>持续时间</t>
   </si>
   <si>
     <t>伤害倍率</t>
@@ -1046,13 +1052,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="28.625" customWidth="1"/>
+    <col min="1" max="6" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5">
+    <row r="1" ht="28" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1068,70 +1074,85 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:5">
+    <row r="2" ht="28" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:5">
+    <row r="3" ht="28" customHeight="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:5">
+    <row r="4" ht="28" customHeight="1" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:5">
+    <row r="5" ht="28" customHeight="1" spans="1:6">
       <c r="B5" s="3">
         <v>1</v>
       </c>
       <c r="C5" s="3">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3">
         <v>1.5</v>
       </c>
-      <c r="D5" s="3">
+      <c r="E5" s="3">
         <v>2</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>16</v>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Skill3KP.xlsx
+++ b/Datas/Skill3KP.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -37,9 +37,6 @@
     <t>ID</t>
   </si>
   <si>
-    <t>Duration</t>
-  </si>
-  <si>
     <t>DamageMultiplier</t>
   </si>
   <si>
@@ -71,9 +68,6 @@
   </si>
   <si>
     <t>参数ID</t>
-  </si>
-  <si>
-    <t>持续时间</t>
   </si>
   <si>
     <t>伤害倍率</t>
@@ -1052,13 +1046,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="6" width="28.625" customWidth="1"/>
+    <col min="1" max="5" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6">
+    <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1074,85 +1068,70 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6">
+    <row r="5" ht="28" customHeight="1" spans="2:5">
       <c r="B5" s="3">
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="D5" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="E5" s="3">
         <v>2</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>18</v>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Skill3KP.xlsx
+++ b/Datas/Skill3KP.xlsx
@@ -79,7 +79,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>示例</t>
+    <t>/</t>
   </si>
 </sst>
 </file>
@@ -1125,10 +1125,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>16</v>

--- a/Datas/Skill3KP.xlsx
+++ b/Datas/Skill3KP.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>##var</t>
   </si>
@@ -43,9 +43,6 @@
     <t>FireRateMultiplier</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -55,9 +52,6 @@
     <t>float</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -74,12 +68,6 @@
   </si>
   <si>
     <t>射速倍率</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>/</t>
   </si>
 </sst>
 </file>
@@ -92,7 +80,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,12 +91,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0F1115"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -592,144 +574,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1046,13 +1025,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="5" width="28.625" customWidth="1"/>
+    <col min="1" max="4" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5">
+    <row r="1" ht="28" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1065,73 +1044,58 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:5">
-      <c r="A3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:4">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="2:5">
-      <c r="B5" s="3">
+    <row r="5" ht="28" customHeight="1" spans="2:4">
+      <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>3</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
